--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N5_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N5_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>56.570969831731</v>
+        <v>9.192782597656288</v>
       </c>
       <c r="D2" t="n">
-        <v>10.96585609973065</v>
+        <v>1.781951616206231</v>
       </c>
       <c r="E2" t="n">
-        <v>12.69241023298219</v>
+        <v>2.062516662859607</v>
       </c>
       <c r="F2" t="n">
-        <v>11.30816507269971</v>
+        <v>1.837576824313703</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>49.09355643198955</v>
+        <v>7.977702920198303</v>
       </c>
       <c r="D3" t="n">
-        <v>10.68877916321597</v>
+        <v>1.736926614022596</v>
       </c>
       <c r="E3" t="n">
-        <v>12.69241023298219</v>
+        <v>2.062516662859607</v>
       </c>
       <c r="F3" t="n">
-        <v>11.30816507269971</v>
+        <v>1.837576824313703</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>29.45884173635853</v>
+        <v>4.787061782158262</v>
       </c>
       <c r="D4" t="n">
-        <v>6.480152399672559</v>
+        <v>1.053024764946791</v>
       </c>
       <c r="E4" t="n">
-        <v>12.69241023298219</v>
+        <v>2.062516662859607</v>
       </c>
       <c r="F4" t="n">
-        <v>11.30816507269971</v>
+        <v>1.837576824313703</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>40.96500284727521</v>
+        <v>6.656812962682221</v>
       </c>
       <c r="D5" t="n">
-        <v>29.36254762161553</v>
+        <v>4.771413988512524</v>
       </c>
       <c r="E5" t="n">
-        <v>12.69241023298219</v>
+        <v>2.062516662859607</v>
       </c>
       <c r="F5" t="n">
-        <v>11.30816507269971</v>
+        <v>1.837576824313703</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>25.27660727445273</v>
+        <v>4.107448682098569</v>
       </c>
       <c r="D6" t="n">
-        <v>14.06255408280506</v>
+        <v>2.285165038455822</v>
       </c>
       <c r="E6" t="n">
-        <v>12.69241023298219</v>
+        <v>2.062516662859607</v>
       </c>
       <c r="F6" t="n">
-        <v>11.30816507269971</v>
+        <v>1.837576824313703</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>23.44025652574124</v>
+        <v>3.809041685432951</v>
       </c>
       <c r="D7" t="n">
-        <v>22.61073610414252</v>
+        <v>3.67424461692316</v>
       </c>
       <c r="E7" t="n">
-        <v>12.69241023298219</v>
+        <v>2.062516662859607</v>
       </c>
       <c r="F7" t="n">
-        <v>11.30816507269971</v>
+        <v>1.837576824313703</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>36.71766455194255</v>
+        <v>5.966620489690664</v>
       </c>
       <c r="D8" t="n">
-        <v>26.8125357864272</v>
+        <v>4.357037065294421</v>
       </c>
       <c r="E8" t="n">
-        <v>12.69241023298219</v>
+        <v>2.062516662859607</v>
       </c>
       <c r="F8" t="n">
-        <v>11.30816507269971</v>
+        <v>1.837576824313703</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>37.08049407997884</v>
+        <v>6.025580287996562</v>
       </c>
       <c r="D9" t="n">
-        <v>25.13130761024491</v>
+        <v>4.083837486664799</v>
       </c>
       <c r="E9" t="n">
-        <v>12.69241023298219</v>
+        <v>2.062516662859607</v>
       </c>
       <c r="F9" t="n">
-        <v>11.30816507269971</v>
+        <v>1.837576824313703</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>51.49462997834398</v>
+        <v>8.367877371480898</v>
       </c>
       <c r="D10" t="n">
-        <v>38.0208182736873</v>
+        <v>6.178382969474186</v>
       </c>
       <c r="E10" t="n">
-        <v>12.69241023298219</v>
+        <v>2.062516662859607</v>
       </c>
       <c r="F10" t="n">
-        <v>11.30816507269971</v>
+        <v>1.837576824313703</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>35.78916834873857</v>
+        <v>5.815739856670018</v>
       </c>
       <c r="D11" t="n">
-        <v>20.16064866558456</v>
+        <v>3.276105408157492</v>
       </c>
       <c r="E11" t="n">
-        <v>12.69241023298219</v>
+        <v>2.062516662859607</v>
       </c>
       <c r="F11" t="n">
-        <v>11.30816507269971</v>
+        <v>1.837576824313703</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>41.80750534907918</v>
+        <v>6.793719619225366</v>
       </c>
       <c r="D12" t="n">
-        <v>34.63948287231234</v>
+        <v>5.628915966750756</v>
       </c>
       <c r="E12" t="n">
-        <v>12.69241023298219</v>
+        <v>2.062516662859607</v>
       </c>
       <c r="F12" t="n">
-        <v>11.30816507269971</v>
+        <v>1.837576824313703</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>54.35789630871927</v>
+        <v>8.833158150166881</v>
       </c>
       <c r="D13" t="n">
-        <v>17.62942204963945</v>
+        <v>2.864781083066411</v>
       </c>
       <c r="E13" t="n">
-        <v>12.69241023298219</v>
+        <v>2.062516662859607</v>
       </c>
       <c r="F13" t="n">
-        <v>11.30816507269971</v>
+        <v>1.837576824313703</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>34.42643814841476</v>
+        <v>5.594296199117399</v>
       </c>
       <c r="D14" t="n">
-        <v>28.37819613590083</v>
+        <v>4.611456872083885</v>
       </c>
       <c r="E14" t="n">
-        <v>12.69241023298219</v>
+        <v>2.062516662859607</v>
       </c>
       <c r="F14" t="n">
-        <v>11.30816507269971</v>
+        <v>1.837576824313703</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>52.67369727252251</v>
+        <v>8.559475806784908</v>
       </c>
       <c r="D15" t="n">
-        <v>44.17251485270258</v>
+        <v>7.178033663564169</v>
       </c>
       <c r="E15" t="n">
-        <v>12.69241023298219</v>
+        <v>2.062516662859607</v>
       </c>
       <c r="F15" t="n">
-        <v>11.30816507269971</v>
+        <v>1.837576824313703</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>52.48366379093645</v>
+        <v>8.528595366027174</v>
       </c>
       <c r="D16" t="n">
-        <v>17.90757733420276</v>
+        <v>2.909981316807948</v>
       </c>
       <c r="E16" t="n">
-        <v>12.69241023298219</v>
+        <v>2.062516662859607</v>
       </c>
       <c r="F16" t="n">
-        <v>11.30816507269971</v>
+        <v>1.837576824313703</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>51.33043069917873</v>
+        <v>8.341194988616545</v>
       </c>
       <c r="D17" t="n">
-        <v>41.469646565952</v>
+        <v>6.738817566967201</v>
       </c>
       <c r="E17" t="n">
-        <v>12.69241023298219</v>
+        <v>2.062516662859607</v>
       </c>
       <c r="F17" t="n">
-        <v>11.30816507269971</v>
+        <v>1.837576824313703</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>64.13928099686436</v>
+        <v>10.42263316199046</v>
       </c>
       <c r="D18" t="n">
-        <v>6.483144870985901</v>
+        <v>1.053511041535209</v>
       </c>
       <c r="E18" t="n">
-        <v>12.69241023298219</v>
+        <v>2.062516662859607</v>
       </c>
       <c r="F18" t="n">
-        <v>11.30816507269971</v>
+        <v>1.837576824313703</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>70.46791746461001</v>
+        <v>11.45103658799913</v>
       </c>
       <c r="D19" t="n">
-        <v>32.36330276987005</v>
+        <v>5.259036700103884</v>
       </c>
       <c r="E19" t="n">
-        <v>12.69241023298219</v>
+        <v>2.062516662859607</v>
       </c>
       <c r="F19" t="n">
-        <v>11.30816507269971</v>
+        <v>1.837576824313703</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
